--- a/huge数据对比/3mz-pite-noname.xlsx
+++ b/huge数据对比/3mz-pite-noname.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\best igl wiki\huge数据对比\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E736D65-A999-4E8E-907D-4133622775E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A513AD8-2C48-4B20-A9D4-B8D0D9419BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31087" yWindow="-109" windowWidth="31196" windowHeight="18974" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,15 +127,15 @@
     <numFmt numFmtId="180" formatCode="0.0%"/>
     <numFmt numFmtId="181" formatCode="[Color10]0.0%;[Red]\-0.0%;0.0%"/>
     <numFmt numFmtId="182" formatCode="0.00_ "/>
-    <numFmt numFmtId="185" formatCode="[Blue]0;[Red]\-0;0"/>
-    <numFmt numFmtId="186" formatCode="[Color10]0;[Blue]\-0;0"/>
-    <numFmt numFmtId="187" formatCode="[Red]0;[Blue]\-0;0"/>
-    <numFmt numFmtId="188" formatCode="[Blue]0.00;[Red]\-0.00;0.00"/>
-    <numFmt numFmtId="189" formatCode="[Blue]0;[Color10]\-0;0"/>
-    <numFmt numFmtId="190" formatCode="[Color10]0.00;[Blue]\-0.00;0.00"/>
-    <numFmt numFmtId="193" formatCode="[Color14]0;[Red]\-0;0"/>
-    <numFmt numFmtId="195" formatCode="[Color14]0.00;[Red]\-0.00;0.00"/>
-    <numFmt numFmtId="196" formatCode="[Red]0;[Color14]\-0;0"/>
+    <numFmt numFmtId="183" formatCode="[Blue]0;[Red]\-0;0"/>
+    <numFmt numFmtId="184" formatCode="[Color10]0;[Blue]\-0;0"/>
+    <numFmt numFmtId="185" formatCode="[Red]0;[Blue]\-0;0"/>
+    <numFmt numFmtId="186" formatCode="[Blue]0.00;[Red]\-0.00;0.00"/>
+    <numFmt numFmtId="187" formatCode="[Blue]0;[Color10]\-0;0"/>
+    <numFmt numFmtId="188" formatCode="[Color10]0.00;[Blue]\-0.00;0.00"/>
+    <numFmt numFmtId="189" formatCode="[Color14]0;[Red]\-0;0"/>
+    <numFmt numFmtId="190" formatCode="[Color14]0.00;[Red]\-0.00;0.00"/>
+    <numFmt numFmtId="191" formatCode="[Red]0;[Color14]\-0;0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -208,7 +208,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -229,13 +232,10 @@
     <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="196" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -529,11 +529,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
       <c r="D1" s="9" t="s">
         <v>0</v>
       </c>
@@ -580,11 +580,11 @@
       <c r="AB1" s="9"/>
     </row>
     <row r="2" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
       <c r="D2" s="11" t="s">
         <v>2</v>
       </c>
@@ -634,9 +634,9 @@
       <c r="AB2" s="9"/>
     </row>
     <row r="3" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
       <c r="D3" s="9" t="s">
         <v>15</v>
       </c>
@@ -667,7 +667,7 @@
         <v>-4568</v>
       </c>
       <c r="M3" s="8">
-        <f t="shared" ref="M2:M3" si="1">J3/E3</f>
+        <f t="shared" ref="M3" si="1">J3/E3</f>
         <v>384.46153846153845</v>
       </c>
       <c r="N3" s="6"/>
@@ -686,9 +686,9 @@
       <c r="AB3" s="9"/>
     </row>
     <row r="4" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
       <c r="D4" s="9" t="s">
         <v>16</v>
       </c>
@@ -738,9 +738,9 @@
       <c r="AB4" s="9"/>
     </row>
     <row r="5" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
       <c r="D5" s="9" t="s">
         <v>17</v>
       </c>
@@ -748,35 +748,35 @@
         <v>21</v>
       </c>
       <c r="F5" s="2">
-        <f>F2-F4</f>
+        <f t="shared" ref="F5:M5" si="3">F2-F4</f>
         <v>15</v>
       </c>
       <c r="G5" s="2">
-        <f>G2-G4</f>
+        <f t="shared" si="3"/>
         <v>-20</v>
       </c>
       <c r="H5" s="5">
-        <f>H2-H4</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="I5" s="4">
-        <f>I2-I4</f>
+        <f t="shared" si="3"/>
         <v>-0.12820512820512819</v>
       </c>
       <c r="J5" s="2">
-        <f>J2-J4</f>
+        <f t="shared" si="3"/>
         <v>-6813</v>
       </c>
       <c r="K5" s="5">
-        <f>K2-K4</f>
+        <f t="shared" si="3"/>
         <v>1733</v>
       </c>
       <c r="L5" s="2">
-        <f>L2-L4</f>
+        <f t="shared" si="3"/>
         <v>-8546</v>
       </c>
       <c r="M5" s="4">
-        <f>M2-M4</f>
+        <f t="shared" si="3"/>
         <v>-262.03846153846149</v>
       </c>
       <c r="N5" s="9"/>
@@ -795,45 +795,45 @@
       <c r="AB5" s="9"/>
     </row>
     <row r="6" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
       <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="13">
-        <f>F3-F4</f>
+      <c r="F6" s="12">
+        <f t="shared" ref="F6:M6" si="4">F3-F4</f>
         <v>2</v>
       </c>
-      <c r="G6" s="13">
-        <f>G3-G4</f>
+      <c r="G6" s="12">
+        <f t="shared" si="4"/>
         <v>-13</v>
       </c>
-      <c r="H6" s="15">
-        <f>H3-H4</f>
+      <c r="H6" s="14">
+        <f t="shared" si="4"/>
         <v>-1</v>
       </c>
-      <c r="I6" s="16">
-        <f>I3-I4</f>
+      <c r="I6" s="15">
+        <f t="shared" si="4"/>
         <v>-0.35897435897435903</v>
       </c>
-      <c r="J6" s="13">
-        <f>J3-J4</f>
+      <c r="J6" s="12">
+        <f t="shared" si="4"/>
         <v>-9123</v>
       </c>
-      <c r="K6" s="15">
-        <f>K3-K4</f>
+      <c r="K6" s="14">
+        <f t="shared" si="4"/>
         <v>-736</v>
       </c>
-      <c r="L6" s="13">
-        <f>L3-L4</f>
+      <c r="L6" s="12">
+        <f t="shared" si="4"/>
         <v>-8387</v>
       </c>
-      <c r="M6" s="16">
-        <f>M3-M4</f>
+      <c r="M6" s="15">
+        <f t="shared" si="4"/>
         <v>-350.88461538461536</v>
       </c>
       <c r="N6" s="6"/>
@@ -852,45 +852,45 @@
       <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
       <c r="D7" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="14">
-        <f>F2-F3</f>
+      <c r="F7" s="13">
+        <f t="shared" ref="F7:M7" si="5">F2-F3</f>
         <v>13</v>
       </c>
-      <c r="G7" s="14">
-        <f>G2-G3</f>
+      <c r="G7" s="13">
+        <f t="shared" si="5"/>
         <v>-7</v>
       </c>
-      <c r="H7" s="17">
-        <f>H2-H3</f>
+      <c r="H7" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I7" s="18">
-        <f>I2-I3</f>
+      <c r="I7" s="17">
+        <f t="shared" si="5"/>
         <v>0.23076923076923084</v>
       </c>
-      <c r="J7" s="14">
-        <f>J2-J3</f>
+      <c r="J7" s="13">
+        <f t="shared" si="5"/>
         <v>2310</v>
       </c>
-      <c r="K7" s="17">
-        <f>K2-K3</f>
+      <c r="K7" s="16">
+        <f t="shared" si="5"/>
         <v>2469</v>
       </c>
-      <c r="L7" s="14">
-        <f>L2-L3</f>
+      <c r="L7" s="13">
+        <f t="shared" si="5"/>
         <v>-159</v>
       </c>
-      <c r="M7" s="18">
-        <f>M2-M3</f>
+      <c r="M7" s="17">
+        <f t="shared" si="5"/>
         <v>88.846153846153868</v>
       </c>
       <c r="N7" s="6"/>
@@ -909,45 +909,45 @@
       <c r="AB7" s="9"/>
     </row>
     <row r="8" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
       <c r="D8" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="19">
-        <f>F2+F3-F4</f>
+      <c r="F8" s="18">
+        <f t="shared" ref="F8:M8" si="6">F2+F3-F4</f>
         <v>29</v>
       </c>
-      <c r="G8" s="19">
-        <f>G2+G3-G4</f>
+      <c r="G8" s="18">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H8" s="21">
-        <f>H2+H3-H4</f>
+      <c r="H8" s="20">
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="I8" s="20">
-        <f>I2+I3-I4</f>
+      <c r="I8" s="19">
+        <f t="shared" si="6"/>
         <v>1.1794871794871795</v>
       </c>
-      <c r="J8" s="19">
-        <f>J2+J3-J4</f>
+      <c r="J8" s="18">
+        <f t="shared" si="6"/>
         <v>3183</v>
       </c>
-      <c r="K8" s="21">
-        <f>K2+K3-K4</f>
+      <c r="K8" s="20">
+        <f t="shared" si="6"/>
         <v>16297</v>
       </c>
-      <c r="L8" s="19">
-        <f>L2+L3-L4</f>
+      <c r="L8" s="18">
+        <f t="shared" si="6"/>
         <v>-13114</v>
       </c>
-      <c r="M8" s="20">
-        <f>M2+M3-M4</f>
+      <c r="M8" s="19">
+        <f t="shared" si="6"/>
         <v>122.42307692307691</v>
       </c>
       <c r="N8" s="7"/>
@@ -966,11 +966,11 @@
       <c r="AB8" s="9"/>
     </row>
     <row r="9" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
       <c r="D9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1017,11 +1017,11 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
       <c r="D10" s="11" t="s">
         <v>2</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>759</v>
       </c>
       <c r="M10" s="8">
-        <f t="shared" ref="M10" si="3">J10/E10</f>
+        <f t="shared" ref="M10" si="7">J10/E10</f>
         <v>429.125</v>
       </c>
       <c r="N10" s="6"/>
@@ -1071,9 +1071,9 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
       <c r="D11" s="11" t="s">
         <v>15</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>-3911</v>
       </c>
       <c r="M11" s="8">
-        <f t="shared" ref="M10:M12" si="4">J11/E11</f>
+        <f t="shared" ref="M11:M12" si="8">J11/E11</f>
         <v>440.22500000000002</v>
       </c>
       <c r="N11" s="6"/>
@@ -1123,9 +1123,9 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
       <c r="D12" s="11" t="s">
         <v>16</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>6139</v>
       </c>
       <c r="M12" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>851.85294117647061</v>
       </c>
       <c r="N12" s="7"/>
@@ -1175,9 +1175,9 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
       <c r="D13" s="11" t="s">
         <v>17</v>
       </c>
@@ -1185,35 +1185,35 @@
         <v>21</v>
       </c>
       <c r="F13" s="2">
-        <f>F10-F12</f>
+        <f t="shared" ref="F13:M13" si="9">F10-F12</f>
         <v>-46</v>
       </c>
       <c r="G13" s="2">
-        <f>G10-G12</f>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="H13" s="5">
-        <f>H10-H12</f>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="I13" s="4">
-        <f>I10-I12</f>
+        <f t="shared" si="9"/>
         <v>-0.65761689291101044</v>
       </c>
       <c r="J13" s="2">
-        <f>J10-J12</f>
+        <f t="shared" si="9"/>
         <v>-11798</v>
       </c>
       <c r="K13" s="5">
-        <f>K10-K12</f>
+        <f t="shared" si="9"/>
         <v>-6418</v>
       </c>
       <c r="L13" s="2">
-        <f>L10-L12</f>
+        <f t="shared" si="9"/>
         <v>-5380</v>
       </c>
       <c r="M13" s="4">
-        <f>M10-M12</f>
+        <f t="shared" si="9"/>
         <v>-422.72794117647061</v>
       </c>
       <c r="N13" s="11"/>
@@ -1232,45 +1232,45 @@
       <c r="AB13" s="11"/>
     </row>
     <row r="14" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
       <c r="D14" s="11" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13">
-        <f>F11-F12</f>
+      <c r="F14" s="12">
+        <f t="shared" ref="F14:M14" si="10">F11-F12</f>
         <v>-25</v>
       </c>
-      <c r="G14" s="13">
-        <f>G11-G12</f>
+      <c r="G14" s="12">
+        <f t="shared" si="10"/>
         <v>-3</v>
       </c>
-      <c r="H14" s="15">
-        <f>H11-H12</f>
+      <c r="H14" s="14">
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="I14" s="16">
-        <f>I11-I12</f>
+      <c r="I14" s="15">
+        <f t="shared" si="10"/>
         <v>-1.003095975232198</v>
       </c>
-      <c r="J14" s="13">
-        <f>J11-J12</f>
+      <c r="J14" s="12">
+        <f t="shared" si="10"/>
         <v>-11354</v>
       </c>
-      <c r="K14" s="15">
-        <f>K11-K12</f>
+      <c r="K14" s="14">
+        <f t="shared" si="10"/>
         <v>-1304</v>
       </c>
-      <c r="L14" s="13">
-        <f>L11-L12</f>
+      <c r="L14" s="12">
+        <f t="shared" si="10"/>
         <v>-10050</v>
       </c>
-      <c r="M14" s="16">
-        <f>M11-M12</f>
+      <c r="M14" s="15">
+        <f t="shared" si="10"/>
         <v>-411.62794117647059</v>
       </c>
       <c r="N14" s="6"/>
@@ -1289,45 +1289,45 @@
       <c r="AB14" s="9"/>
     </row>
     <row r="15" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
       <c r="D15" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <f>F10-F11</f>
+      <c r="F15" s="13">
+        <f t="shared" ref="F15:M15" si="11">F10-F11</f>
         <v>-21</v>
       </c>
-      <c r="G15" s="14">
-        <f>G10-G11</f>
+      <c r="G15" s="13">
+        <f t="shared" si="11"/>
         <v>36</v>
       </c>
-      <c r="H15" s="17">
-        <f>H10-H11</f>
+      <c r="H15" s="16">
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="I15" s="18">
-        <f>I10-I11</f>
+      <c r="I15" s="17">
+        <f t="shared" si="11"/>
         <v>0.34547908232118751</v>
       </c>
-      <c r="J15" s="14">
-        <f>J10-J11</f>
+      <c r="J15" s="13">
+        <f t="shared" si="11"/>
         <v>-444</v>
       </c>
-      <c r="K15" s="17">
-        <f>K10-K11</f>
+      <c r="K15" s="16">
+        <f t="shared" si="11"/>
         <v>-5114</v>
       </c>
-      <c r="L15" s="14">
-        <f>L10-L11</f>
+      <c r="L15" s="13">
+        <f t="shared" si="11"/>
         <v>4670</v>
       </c>
-      <c r="M15" s="18">
-        <f>M10-M11</f>
+      <c r="M15" s="17">
+        <f t="shared" si="11"/>
         <v>-11.100000000000023</v>
       </c>
       <c r="N15" s="6"/>
@@ -1346,45 +1346,45 @@
       <c r="AB15" s="9"/>
     </row>
     <row r="16" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
       <c r="D16" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="19">
-        <f>F10+F11-F12</f>
+      <c r="F16" s="18">
+        <f t="shared" ref="F16:M16" si="12">F10+F11-F12</f>
         <v>-13</v>
       </c>
-      <c r="G16" s="19">
-        <f>G10+G11-G12</f>
+      <c r="G16" s="18">
+        <f t="shared" si="12"/>
         <v>58</v>
       </c>
-      <c r="H16" s="21">
-        <f>H10+H11-H12</f>
+      <c r="H16" s="20">
+        <f t="shared" si="12"/>
         <v>43</v>
       </c>
-      <c r="I16" s="20">
-        <f>I10+I11-I12</f>
+      <c r="I16" s="19">
+        <f t="shared" si="12"/>
         <v>0.86869889656267407</v>
       </c>
-      <c r="J16" s="19">
-        <f>J10+J11-J12</f>
+      <c r="J16" s="18">
+        <f t="shared" si="12"/>
         <v>5811</v>
       </c>
-      <c r="K16" s="21">
-        <f>K10+K11-K12</f>
+      <c r="K16" s="20">
+        <f t="shared" si="12"/>
         <v>15102</v>
       </c>
-      <c r="L16" s="19">
-        <f>L10+L11-L12</f>
+      <c r="L16" s="18">
+        <f t="shared" si="12"/>
         <v>-9291</v>
       </c>
-      <c r="M16" s="20">
-        <f>M10+M11-M12</f>
+      <c r="M16" s="19">
+        <f t="shared" si="12"/>
         <v>17.497058823529414</v>
       </c>
       <c r="N16" s="7"/>
@@ -1403,11 +1403,11 @@
       <c r="AB16" s="9"/>
     </row>
     <row r="17" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
       <c r="D17" s="9" t="s">
         <v>0</v>
       </c>
@@ -1454,11 +1454,11 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="11" t="s">
         <v>2</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>41</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" ref="I18" si="5">(F18+G18)/H18</f>
+        <f t="shared" ref="I18" si="13">(F18+G18)/H18</f>
         <v>1.975609756097561</v>
       </c>
       <c r="J18" s="11">
@@ -1485,11 +1485,11 @@
         <v>24123</v>
       </c>
       <c r="L18" s="11">
-        <f t="shared" ref="L18" si="6">J18-K18</f>
+        <f t="shared" ref="L18" si="14">J18-K18</f>
         <v>-973</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" ref="M18" si="7">J18/E18</f>
+        <f t="shared" ref="M18" si="15">J18/E18</f>
         <v>564.63414634146341</v>
       </c>
       <c r="N18" s="6"/>
@@ -1508,9 +1508,9 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
       <c r="D19" s="11" t="s">
         <v>15</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>40</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" ref="I18:I19" si="8">(F19+G19)/H19</f>
+        <f t="shared" ref="I19" si="16">(F19+G19)/H19</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="J19" s="11">
@@ -1537,11 +1537,11 @@
         <v>22313</v>
       </c>
       <c r="L19" s="11">
-        <f t="shared" ref="L18:L19" si="9">J19-K19</f>
+        <f t="shared" ref="L19" si="17">J19-K19</f>
         <v>-1173</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" ref="M18:M20" si="10">J19/E19</f>
+        <f t="shared" ref="M19:M20" si="18">J19/E19</f>
         <v>528.5</v>
       </c>
       <c r="N19" s="6"/>
@@ -1560,9 +1560,9 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
       <c r="D20" s="11" t="s">
         <v>16</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>13528</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>1047.3902439024391</v>
       </c>
       <c r="N20" s="7"/>
@@ -1612,9 +1612,9 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
       <c r="D21" s="11" t="s">
         <v>17</v>
       </c>
@@ -1622,35 +1622,35 @@
         <v>21</v>
       </c>
       <c r="F21" s="2">
-        <f>F18-F20</f>
+        <f t="shared" ref="F21:M21" si="19">F18-F20</f>
         <v>-27</v>
       </c>
       <c r="G21" s="2">
-        <f>G18-G20</f>
+        <f t="shared" si="19"/>
         <v>-13</v>
       </c>
       <c r="H21" s="5">
-        <f>H18-H20</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I21" s="4">
-        <f>I18-I20</f>
+        <f t="shared" si="19"/>
         <v>-0.97560975609756095</v>
       </c>
       <c r="J21" s="2">
-        <f>J18-J20</f>
+        <f t="shared" si="19"/>
         <v>-19793</v>
       </c>
       <c r="K21" s="5">
-        <f>K18-K20</f>
+        <f t="shared" si="19"/>
         <v>-5292</v>
       </c>
       <c r="L21" s="2">
-        <f>L18-L20</f>
+        <f t="shared" si="19"/>
         <v>-14501</v>
       </c>
       <c r="M21" s="4">
-        <f>M18-M20</f>
+        <f t="shared" si="19"/>
         <v>-482.75609756097572</v>
       </c>
       <c r="N21" s="11"/>
@@ -1669,45 +1669,45 @@
       <c r="AB21" s="11"/>
     </row>
     <row r="22" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
       <c r="D22" s="11" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13">
-        <f>F19-F20</f>
+      <c r="F22" s="12">
+        <f t="shared" ref="F22:M22" si="20">F19-F20</f>
         <v>-22</v>
       </c>
-      <c r="G22" s="13">
-        <f>G19-G20</f>
+      <c r="G22" s="12">
+        <f t="shared" si="20"/>
         <v>-11</v>
       </c>
-      <c r="H22" s="15">
-        <f>H19-H20</f>
+      <c r="H22" s="14">
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="I22" s="16">
-        <f>I19-I20</f>
+      <c r="I22" s="15">
+        <f t="shared" si="20"/>
         <v>-0.75121951219512173</v>
       </c>
-      <c r="J22" s="13">
-        <f>J19-J20</f>
+      <c r="J22" s="12">
+        <f t="shared" si="20"/>
         <v>-21803</v>
       </c>
-      <c r="K22" s="15">
-        <f>K19-K20</f>
+      <c r="K22" s="14">
+        <f t="shared" si="20"/>
         <v>-7102</v>
       </c>
-      <c r="L22" s="13">
-        <f>L19-L20</f>
+      <c r="L22" s="12">
+        <f t="shared" si="20"/>
         <v>-14701</v>
       </c>
-      <c r="M22" s="16">
-        <f>M19-M20</f>
+      <c r="M22" s="15">
+        <f t="shared" si="20"/>
         <v>-518.89024390243912</v>
       </c>
       <c r="N22" s="6"/>
@@ -1726,45 +1726,45 @@
       <c r="AB22" s="9"/>
     </row>
     <row r="23" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
       <c r="D23" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="14">
-        <f>F18-F19</f>
+      <c r="F23" s="13">
+        <f t="shared" ref="F23:M23" si="21">F18-F19</f>
         <v>-5</v>
       </c>
-      <c r="G23" s="14">
-        <f>G18-G19</f>
+      <c r="G23" s="13">
+        <f t="shared" si="21"/>
         <v>-2</v>
       </c>
-      <c r="H23" s="17">
-        <f>H18-H19</f>
+      <c r="H23" s="16">
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="I23" s="18">
-        <f>I18-I19</f>
+      <c r="I23" s="17">
+        <f t="shared" si="21"/>
         <v>-0.22439024390243922</v>
       </c>
-      <c r="J23" s="14">
-        <f>J18-J19</f>
+      <c r="J23" s="13">
+        <f t="shared" si="21"/>
         <v>2010</v>
       </c>
-      <c r="K23" s="17">
-        <f>K18-K19</f>
+      <c r="K23" s="16">
+        <f t="shared" si="21"/>
         <v>1810</v>
       </c>
-      <c r="L23" s="14">
-        <f>L18-L19</f>
+      <c r="L23" s="13">
+        <f t="shared" si="21"/>
         <v>200</v>
       </c>
-      <c r="M23" s="18">
-        <f>M18-M19</f>
+      <c r="M23" s="17">
+        <f t="shared" si="21"/>
         <v>36.134146341463406</v>
       </c>
       <c r="N23" s="6"/>
@@ -1783,45 +1783,45 @@
       <c r="AB23" s="9"/>
     </row>
     <row r="24" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
       <c r="D24" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="19">
-        <f>F18+F19-F20</f>
+      <c r="F24" s="18">
+        <f t="shared" ref="F24:M24" si="22">F18+F19-F20</f>
         <v>16</v>
       </c>
-      <c r="G24" s="19">
-        <f>G18+G19-G20</f>
+      <c r="G24" s="18">
+        <f t="shared" si="22"/>
         <v>32</v>
       </c>
-      <c r="H24" s="21">
-        <f>H18+H19-H20</f>
+      <c r="H24" s="20">
+        <f t="shared" si="22"/>
         <v>40</v>
       </c>
-      <c r="I24" s="20">
-        <f>I18+I19-I20</f>
+      <c r="I24" s="19">
+        <f t="shared" si="22"/>
         <v>1.2243902439024392</v>
       </c>
-      <c r="J24" s="19">
-        <f>J18+J19-J20</f>
+      <c r="J24" s="18">
+        <f t="shared" si="22"/>
         <v>1347</v>
       </c>
-      <c r="K24" s="21">
-        <f>K18+K19-K20</f>
+      <c r="K24" s="20">
+        <f t="shared" si="22"/>
         <v>17021</v>
       </c>
-      <c r="L24" s="19">
-        <f>L18+L19-L20</f>
+      <c r="L24" s="18">
+        <f t="shared" si="22"/>
         <v>-15674</v>
       </c>
-      <c r="M24" s="20">
-        <f>M18+M19-M20</f>
+      <c r="M24" s="19">
+        <f t="shared" si="22"/>
         <v>45.743902439024168</v>
       </c>
       <c r="N24" s="7"/>
@@ -1840,9 +1840,9 @@
       <c r="AB24" s="9"/>
     </row>
     <row r="25" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1869,9 +1869,9 @@
       <c r="AB25" s="1"/>
     </row>
     <row r="26" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
       <c r="D26" s="9"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1898,9 +1898,9 @@
       <c r="AB26" s="1"/>
     </row>
     <row r="27" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
       <c r="D27" s="9"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -1927,9 +1927,9 @@
       <c r="AB27" s="1"/>
     </row>
     <row r="28" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
       <c r="D28" s="9"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1956,9 +1956,9 @@
       <c r="AB28" s="1"/>
     </row>
     <row r="29" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -1985,9 +1985,9 @@
       <c r="AB29" s="9"/>
     </row>
     <row r="30" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
@@ -2014,9 +2014,9 @@
       <c r="AB30" s="9"/>
     </row>
     <row r="31" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
@@ -2043,9 +2043,9 @@
       <c r="AB31" s="9"/>
     </row>
     <row r="32" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
       <c r="D32" s="9"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -2072,9 +2072,9 @@
       <c r="AB32" s="9"/>
     </row>
     <row r="33" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
@@ -2101,9 +2101,9 @@
       <c r="AB33" s="9"/>
     </row>
     <row r="34" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
@@ -2130,9 +2130,9 @@
       <c r="AB34" s="9"/>
     </row>
     <row r="35" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
       <c r="D35" s="9"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -2159,9 +2159,9 @@
       <c r="AB35" s="9"/>
     </row>
     <row r="36" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
@@ -2188,9 +2188,9 @@
       <c r="AB36" s="9"/>
     </row>
     <row r="37" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
@@ -2217,9 +2217,9 @@
       <c r="AB37" s="9"/>
     </row>
     <row r="38" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
@@ -2246,9 +2246,9 @@
       <c r="AB38" s="9"/>
     </row>
     <row r="39" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
       <c r="D39" s="9"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -2275,9 +2275,9 @@
       <c r="AB39" s="9"/>
     </row>
     <row r="40" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
@@ -2333,9 +2333,9 @@
       <c r="AB41" s="9"/>
     </row>
     <row r="42" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
@@ -2362,9 +2362,9 @@
       <c r="AB42" s="9"/>
     </row>
     <row r="43" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
@@ -2391,9 +2391,9 @@
       <c r="AB43" s="9"/>
     </row>
     <row r="44" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
       <c r="D44" s="9"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -2420,9 +2420,9 @@
       <c r="AB44" s="9"/>
     </row>
     <row r="45" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
@@ -2449,9 +2449,9 @@
       <c r="AB45" s="9"/>
     </row>
     <row r="46" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
@@ -2478,9 +2478,9 @@
       <c r="AB46" s="9"/>
     </row>
     <row r="47" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
@@ -2507,9 +2507,9 @@
       <c r="AB47" s="9"/>
     </row>
     <row r="48" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
       <c r="D48" s="9"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -2536,9 +2536,9 @@
       <c r="AB48" s="9"/>
     </row>
     <row r="49" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
+      <c r="A49" s="21"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
@@ -2565,9 +2565,9 @@
       <c r="AB49" s="9"/>
     </row>
     <row r="50" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
+      <c r="A50" s="21"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -2594,9 +2594,9 @@
       <c r="AB50" s="1"/>
     </row>
     <row r="51" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -2623,9 +2623,9 @@
       <c r="AB51" s="1"/>
     </row>
     <row r="52" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
       <c r="D52" s="1"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -2652,9 +2652,9 @@
       <c r="AB52" s="1"/>
     </row>
     <row r="53" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
+      <c r="A53" s="21"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
